--- a/data/bulk-upload-users/upload-users-missing-fields.xlsx
+++ b/data/bulk-upload-users/upload-users-missing-fields.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F9885-FD76-4993-BEB4-AEB2D6045BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A375A3-8250-4BB5-B186-DAE763E69399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>no</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>lastName</t>
   </si>
@@ -29,22 +26,22 @@
     <t>idType</t>
   </si>
   <si>
-    <t>idNumber</t>
-  </si>
-  <si>
     <t>phoneNumber</t>
   </si>
   <si>
     <t>NID</t>
   </si>
   <si>
-    <t>Panha</t>
-  </si>
-  <si>
-    <t>ID0011223ABCD</t>
-  </si>
-  <si>
-    <t>0971234567</t>
+    <t>remark:</t>
+  </si>
+  <si>
+    <t>PASSPORT</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>David</t>
   </si>
 </sst>
 </file>
@@ -428,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
@@ -439,46 +436,66 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="C2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
       <c r="F3" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>123456789</v>
+      </c>
+      <c r="F6">
+        <v>92234234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>123456789</v>
+      </c>
+      <c r="F7">
+        <v>92234234</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
